--- a/A14 311 CLC producción.xlsx
+++ b/A14 311 CLC producción.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/00b6926b2e2f81b4/Documentos/Proyectos/25.2/25.2 - Custom Extensiones/Payroll/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="333" documentId="13_ncr:1_{EE092345-9921-432B-9AA1-E6BA4CEBEE99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B385D549-3C4F-45EA-8E72-49F5CD040AB1}"/>
+  <xr:revisionPtr revIDLastSave="383" documentId="13_ncr:1_{EE092345-9921-432B-9AA1-E6BA4CEBEE99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3EF8E58-865F-42C2-B7E7-9CD5FC24ECE5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="599" xr2:uid="{384BEB01-60EC-4FC9-B665-3C784E2A368C}"/>
   </bookViews>
@@ -19,8 +19,7 @@
     <sheet name="Hoja3" sheetId="17" r:id="rId4"/>
     <sheet name="Hoja4" sheetId="18" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029" calcCompleted="0"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1387,7 +1386,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1690,6 +1689,15 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1712,12 +1720,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1743,10 +1745,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2050,12 +2048,12 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" style="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10" style="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" style="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" style="18" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.85546875" style="18" bestFit="1" customWidth="1"/>
     <col min="6" max="10" width="13.5703125" style="18" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="12.5703125" style="18" bestFit="1" customWidth="1"/>
+    <col min="11" max="15" width="12.5703125" style="18" customWidth="1"/>
     <col min="16" max="16" width="10.85546875" style="18" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="17.5703125" style="18" customWidth="1"/>
     <col min="18" max="18" width="13.42578125" style="18" customWidth="1"/>
@@ -3141,29 +3139,29 @@
     </row>
     <row r="12" spans="1:26" ht="14.25" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:26" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="104" t="s">
+      <c r="C13" s="107" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="105"/>
-      <c r="E13" s="105"/>
-      <c r="F13" s="105"/>
-      <c r="G13" s="105"/>
-      <c r="H13" s="106"/>
-      <c r="J13" s="104" t="s">
+      <c r="D13" s="108"/>
+      <c r="E13" s="108"/>
+      <c r="F13" s="108"/>
+      <c r="G13" s="108"/>
+      <c r="H13" s="109"/>
+      <c r="J13" s="107" t="s">
         <v>27</v>
       </c>
-      <c r="K13" s="105"/>
-      <c r="L13" s="105"/>
-      <c r="M13" s="105"/>
-      <c r="N13" s="105"/>
-      <c r="O13" s="106"/>
-      <c r="P13" s="109" t="s">
+      <c r="K13" s="108"/>
+      <c r="L13" s="108"/>
+      <c r="M13" s="108"/>
+      <c r="N13" s="108"/>
+      <c r="O13" s="109"/>
+      <c r="P13" s="112" t="s">
         <v>44</v>
       </c>
-      <c r="Q13" s="110"/>
-      <c r="R13" s="110"/>
-      <c r="S13" s="110"/>
-      <c r="T13" s="111"/>
+      <c r="Q13" s="113"/>
+      <c r="R13" s="113"/>
+      <c r="S13" s="113"/>
+      <c r="T13" s="114"/>
       <c r="U13" s="18"/>
     </row>
     <row r="14" spans="1:26" s="15" customFormat="1" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -3831,7 +3829,10 @@
     </row>
     <row r="26" spans="1:26" ht="108" x14ac:dyDescent="0.25">
       <c r="A26" s="35"/>
-      <c r="B26" s="5"/>
+      <c r="B26" s="5">
+        <f>+F26/30</f>
+        <v>267666.66666666669</v>
+      </c>
       <c r="C26" s="19"/>
       <c r="D26" s="83"/>
       <c r="E26" s="36" t="s">
@@ -3875,7 +3876,7 @@
         <f>+K25/30</f>
         <v>31710.400000000001</v>
       </c>
-      <c r="Q26" s="112">
+      <c r="Q26" s="104">
         <f>+O23*0.3</f>
         <v>3457348.6550400001</v>
       </c>
@@ -3960,9 +3961,10 @@
       <c r="M28" s="85"/>
       <c r="N28" s="85"/>
       <c r="O28" s="85"/>
-      <c r="P28" s="17"/>
+      <c r="P28" s="106"/>
       <c r="Q28" s="17"/>
-      <c r="R28" s="100" t="s">
+      <c r="R28" s="17"/>
+      <c r="S28" s="100" t="s">
         <v>142</v>
       </c>
     </row>
@@ -4004,7 +4006,7 @@
         <f t="shared" si="3"/>
         <v>80581.679999999993</v>
       </c>
-      <c r="M29" s="113">
+      <c r="M29" s="105">
         <f t="shared" si="3"/>
         <v>75545.37</v>
       </c>
@@ -4016,8 +4018,13 @@
         <f t="shared" si="3"/>
         <v>70508.97</v>
       </c>
-      <c r="P29" s="13"/>
-      <c r="Q29" s="17"/>
+      <c r="P29" s="18">
+        <v>70508.97</v>
+      </c>
+      <c r="Q29" s="13">
+        <f>+N29-P29</f>
+        <v>0</v>
+      </c>
       <c r="R29" s="17"/>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.25">
@@ -4058,7 +4065,7 @@
         <f t="shared" si="4"/>
         <v>51780</v>
       </c>
-      <c r="M30" s="113">
+      <c r="M30" s="105">
         <f t="shared" si="4"/>
         <v>48543.74</v>
       </c>
@@ -4070,16 +4077,19 @@
         <f t="shared" si="4"/>
         <v>45307.5</v>
       </c>
-      <c r="P30" s="33">
-        <f>+O30+O31+O32+O33</f>
-        <v>109292.2895</v>
-      </c>
-      <c r="Q30" s="87"/>
-      <c r="R30" s="97">
+      <c r="P30" s="18">
+        <v>45307.5</v>
+      </c>
+      <c r="Q30" s="13">
+        <f t="shared" ref="Q30:Q42" si="5">+N30-P30</f>
+        <v>0</v>
+      </c>
+      <c r="R30" s="87"/>
+      <c r="S30" s="97">
         <f>(+B18/1000*I18*C9*R14)*0.9/I18*I15</f>
         <v>1374614.5046399997</v>
       </c>
-      <c r="S30" s="87"/>
+      <c r="T30" s="87"/>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
@@ -4096,19 +4106,19 @@
         <v>46200</v>
       </c>
       <c r="G31" s="46">
-        <f t="shared" ref="G31:O31" si="5">G$25/30*($E29+$E30)*$E31*$C$10</f>
+        <f t="shared" ref="G31:O31" si="6">G$25/30*($E29+$E30)*$E31*$C$10</f>
         <v>41250</v>
       </c>
       <c r="H31" s="46">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>82500</v>
       </c>
       <c r="I31" s="46">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>41250</v>
       </c>
       <c r="J31" s="46">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>26161.08</v>
       </c>
       <c r="K31" s="46">
@@ -4116,31 +4126,34 @@
         <v>26161.08</v>
       </c>
       <c r="L31" s="46">
+        <f t="shared" si="6"/>
+        <v>24622.18</v>
+      </c>
+      <c r="M31" s="105">
+        <f t="shared" si="6"/>
+        <v>23083.307499999999</v>
+      </c>
+      <c r="N31" s="46">
+        <f t="shared" si="6"/>
+        <v>21544.407499999998</v>
+      </c>
+      <c r="O31" s="46">
+        <f t="shared" si="6"/>
+        <v>21544.407499999998</v>
+      </c>
+      <c r="P31" s="18">
+        <v>15511.97</v>
+      </c>
+      <c r="Q31" s="13">
         <f t="shared" si="5"/>
-        <v>24622.18</v>
-      </c>
-      <c r="M31" s="113">
-        <f t="shared" si="5"/>
-        <v>23083.307499999999</v>
-      </c>
-      <c r="N31" s="46">
-        <f t="shared" si="5"/>
-        <v>21544.407499999998</v>
-      </c>
-      <c r="O31" s="46">
-        <f t="shared" si="5"/>
-        <v>21544.407499999998</v>
-      </c>
-      <c r="P31" s="33">
-        <f>+P30/70*75</f>
-        <v>117098.88160714284</v>
-      </c>
-      <c r="Q31" s="87"/>
-      <c r="R31" s="30">
-        <f>(+R30-R18)*C10</f>
+        <v>6032.4374999999982</v>
+      </c>
+      <c r="R31" s="87"/>
+      <c r="S31" s="30">
+        <f>(+S30-R18)*C10</f>
         <v>92430.975311999922</v>
       </c>
-      <c r="S31" s="87"/>
+      <c r="T31" s="87"/>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
@@ -4153,56 +4166,59 @@
         <v>0.6</v>
       </c>
       <c r="F32" s="46">
-        <f t="shared" ref="F32:O32" si="6">+F29*$E32</f>
+        <f t="shared" ref="F32:O32" si="7">+F29*$E32</f>
         <v>162000</v>
       </c>
       <c r="G32" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>81000</v>
       </c>
       <c r="H32" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>162000</v>
       </c>
       <c r="I32" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>81000</v>
       </c>
       <c r="J32" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>51370.847999999998</v>
       </c>
       <c r="K32" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>51370.847999999998</v>
       </c>
       <c r="L32" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>48349.007999999994</v>
       </c>
-      <c r="M32" s="113">
-        <f t="shared" si="6"/>
+      <c r="M32" s="105">
+        <f t="shared" si="7"/>
         <v>45327.221999999994</v>
       </c>
       <c r="N32" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>42305.381999999998</v>
       </c>
       <c r="O32" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>42305.381999999998</v>
       </c>
-      <c r="P32" s="33">
-        <f>+P31-P30</f>
-        <v>7806.5921071428456</v>
-      </c>
-      <c r="Q32" s="88" t="s">
+      <c r="P32" s="18">
+        <v>42305.38</v>
+      </c>
+      <c r="Q32" s="13">
+        <f t="shared" si="5"/>
+        <v>2.0000000004074536E-3</v>
+      </c>
+      <c r="R32" s="88" t="s">
         <v>52</v>
       </c>
-      <c r="R32" s="87"/>
       <c r="S32" s="87"/>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T32" s="87"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
         <v>56</v>
       </c>
@@ -4237,7 +4253,7 @@
         <f>50/70*80*$E33*$C$10</f>
         <v>154.28571428571431</v>
       </c>
-      <c r="M33" s="113">
+      <c r="M33" s="105">
         <f>50/70*75*$E33*$C$10</f>
         <v>144.64285714285714</v>
       </c>
@@ -4249,12 +4265,18 @@
         <f>50*$E33*$C$10</f>
         <v>135</v>
       </c>
-      <c r="P33" s="30"/>
-      <c r="Q33" s="87"/>
+      <c r="P33" s="18">
+        <v>135</v>
+      </c>
+      <c r="Q33" s="13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="R33" s="87"/>
       <c r="S33" s="87"/>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T33" s="87"/>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>57</v>
       </c>
@@ -4277,7 +4299,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="46">
-        <f t="shared" ref="J34:O34" si="7">+$B$20/1000*$E34*$C$10</f>
+        <f t="shared" ref="J34:O34" si="8">+$B$20/1000*$E34*$C$10</f>
         <v>53249.817599999995</v>
       </c>
       <c r="K34" s="46">
@@ -4285,26 +4307,33 @@
         <v>53249.817599999995</v>
       </c>
       <c r="L34" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>53249.817599999995</v>
       </c>
-      <c r="M34" s="113">
-        <f t="shared" si="7"/>
+      <c r="M34" s="105">
+        <f t="shared" si="8"/>
         <v>53249.817599999995</v>
       </c>
       <c r="N34" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>53249.817599999995</v>
       </c>
       <c r="O34" s="46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>53249.817599999995</v>
       </c>
-      <c r="P34" s="30"/>
-      <c r="Q34" s="87"/>
-      <c r="S34" s="87"/>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P34" s="18">
+        <v>53247.5</v>
+      </c>
+      <c r="Q34" s="13">
+        <f t="shared" si="5"/>
+        <v>2.3175999999948544</v>
+      </c>
+      <c r="R34" s="87"/>
+      <c r="S34" s="18"/>
+      <c r="T34" s="87"/>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
         <v>58</v>
       </c>
@@ -4344,15 +4373,18 @@
       <c r="O35" s="46">
         <v>0</v>
       </c>
-      <c r="P35" s="30"/>
-      <c r="Q35" s="87"/>
-      <c r="R35" s="97">
+      <c r="Q35" s="13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R35" s="87"/>
+      <c r="S35" s="97">
         <f>+R15/0.3</f>
         <v>7431767.452800001</v>
       </c>
-      <c r="S35" s="87"/>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T35" s="87"/>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
         <v>59</v>
       </c>
@@ -4381,28 +4413,35 @@
         <v>668859.07075200009</v>
       </c>
       <c r="L36" s="46">
-        <f t="shared" ref="L36:M39" si="8">+$S15*$C$10</f>
+        <f t="shared" ref="L36:M39" si="9">+$S15*$C$10</f>
         <v>601973.16367679997</v>
       </c>
-      <c r="M36" s="113">
-        <f t="shared" si="8"/>
+      <c r="M36" s="105">
+        <f t="shared" si="9"/>
         <v>601973.16367679997</v>
       </c>
       <c r="N36" s="46">
-        <f t="shared" ref="N36:O39" si="9">+$T15*$C$10</f>
+        <f t="shared" ref="N36:O39" si="10">+$T15*$C$10</f>
         <v>568530.21013920009</v>
       </c>
       <c r="O36" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>568530.21013920009</v>
       </c>
-      <c r="P36" s="30"/>
-      <c r="Q36" s="87" t="s">
+      <c r="P36" s="18">
+        <v>568530.21</v>
+      </c>
+      <c r="Q36" s="13">
+        <f t="shared" si="5"/>
+        <v>1.392001286149025E-4</v>
+      </c>
+      <c r="R36" s="87" t="s">
         <v>139</v>
       </c>
-      <c r="S36" s="87"/>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S36" s="18"/>
+      <c r="T36" s="87"/>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
         <v>60</v>
       </c>
@@ -4423,40 +4462,46 @@
         <v>0</v>
       </c>
       <c r="J37" s="46">
-        <f t="shared" ref="J37" si="10">+$R16*$C$10</f>
+        <f t="shared" ref="J37" si="11">+$R16*$C$10</f>
         <v>611435.42064000003</v>
       </c>
       <c r="K37" s="46">
-        <f t="shared" ref="K37" si="11">+$R16*$C$10</f>
+        <f t="shared" ref="K37" si="12">+$R16*$C$10</f>
         <v>611435.42064000003</v>
       </c>
       <c r="L37" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>550291.87857599999</v>
       </c>
-      <c r="M37" s="113">
-        <f t="shared" si="8"/>
+      <c r="M37" s="105">
+        <f t="shared" si="9"/>
         <v>550291.87857599999</v>
       </c>
       <c r="N37" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>519720.10754400009</v>
       </c>
       <c r="O37" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>519720.10754400009</v>
       </c>
-      <c r="P37" s="30"/>
-      <c r="Q37" s="17">
+      <c r="P37" s="18">
+        <v>519720.11</v>
+      </c>
+      <c r="Q37" s="13">
+        <f t="shared" si="5"/>
+        <v>-2.4559999001212418E-3</v>
+      </c>
+      <c r="R37" s="17">
         <f>($B15/1000*$I15*$C$9*R$14)*0.9</f>
         <v>2229530.2358400002</v>
       </c>
-      <c r="R37" s="98" t="s">
+      <c r="S37" s="98" t="s">
         <v>137</v>
       </c>
-      <c r="S37" s="87"/>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T37" s="87"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
         <v>61</v>
       </c>
@@ -4477,40 +4522,43 @@
         <v>0</v>
       </c>
       <c r="J38" s="46">
-        <f t="shared" ref="J38" si="12">+$R17*$C$10</f>
+        <f t="shared" ref="J38" si="13">+$R17*$C$10</f>
         <v>0</v>
       </c>
       <c r="K38" s="46">
-        <f t="shared" ref="K38" si="13">+$R17*$C$10</f>
+        <f t="shared" ref="K38" si="14">+$R17*$C$10</f>
         <v>0</v>
       </c>
       <c r="L38" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M38" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="N38" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O38" s="46">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="P38" s="30"/>
-      <c r="Q38" s="17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Q38" s="13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R38" s="17">
         <f>+$R15*$C$10</f>
         <v>668859.07075200009</v>
       </c>
-      <c r="R38" s="98" t="s">
+      <c r="S38" s="98" t="s">
         <v>138</v>
       </c>
-      <c r="S38" s="87"/>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T38" s="87"/>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
         <v>62</v>
       </c>
@@ -4531,35 +4579,41 @@
         <v>0</v>
       </c>
       <c r="J39" s="46">
-        <f t="shared" ref="J39" si="14">+$R18*$C$10</f>
+        <f t="shared" ref="J39" si="15">+$R18*$C$10</f>
         <v>319953.37607999996</v>
       </c>
       <c r="K39" s="46">
-        <f t="shared" ref="K39" si="15">+$R18*$C$10</f>
+        <f t="shared" ref="K39" si="16">+$R18*$C$10</f>
         <v>319953.37607999996</v>
       </c>
       <c r="L39" s="46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>287958.03847199999</v>
       </c>
-      <c r="M39" s="113">
-        <f t="shared" si="8"/>
+      <c r="M39" s="105">
+        <f t="shared" si="9"/>
         <v>287958.03847199999</v>
       </c>
       <c r="N39" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>271960.36966799997</v>
       </c>
       <c r="O39" s="46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>271960.36966799997</v>
       </c>
-      <c r="P39" s="30"/>
-      <c r="Q39" s="87"/>
+      <c r="P39" s="18">
+        <v>271960.37</v>
+      </c>
+      <c r="Q39" s="13">
+        <f t="shared" si="5"/>
+        <v>-3.3200002508237958E-4</v>
+      </c>
       <c r="R39" s="87"/>
       <c r="S39" s="87"/>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T39" s="87"/>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
         <v>63</v>
       </c>
@@ -4603,12 +4657,18 @@
         <f>+($T$21-$T$18)*$C$10</f>
         <v>78566.329015199983</v>
       </c>
-      <c r="P40" s="30"/>
-      <c r="Q40" s="87"/>
+      <c r="P40" s="18">
+        <v>78568.61</v>
+      </c>
+      <c r="Q40" s="13">
+        <f t="shared" si="5"/>
+        <v>-2.2809848000179045</v>
+      </c>
       <c r="R40" s="87"/>
       <c r="S40" s="87"/>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T40" s="87"/>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>28</v>
       </c>
@@ -4629,35 +4689,41 @@
         <v>0</v>
       </c>
       <c r="J41" s="46">
-        <f t="shared" ref="J41:O41" si="16">(J29+J34)*-1</f>
+        <f t="shared" ref="J41:O41" si="17">(J29+J34)*-1</f>
         <v>-138867.8976</v>
       </c>
       <c r="K41" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-138867.8976</v>
       </c>
       <c r="L41" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-133831.4976</v>
       </c>
-      <c r="M41" s="113">
-        <f t="shared" si="16"/>
+      <c r="M41" s="105">
+        <f t="shared" si="17"/>
         <v>-128795.18759999999</v>
       </c>
       <c r="N41" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-123758.7876</v>
       </c>
       <c r="O41" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-123758.7876</v>
       </c>
-      <c r="P41" s="30"/>
-      <c r="Q41" s="87"/>
+      <c r="P41" s="18">
+        <v>-123758.78</v>
+      </c>
+      <c r="Q41" s="13">
+        <f t="shared" si="5"/>
+        <v>-7.5999999971827492E-3</v>
+      </c>
       <c r="R41" s="87"/>
       <c r="S41" s="87"/>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T41" s="87"/>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
         <v>82</v>
       </c>
@@ -4668,54 +4734,60 @@
         <v>1</v>
       </c>
       <c r="F42" s="46">
-        <f t="shared" ref="F42:O42" si="17">(F29+F30+F31+F32+F33+F34+F36+F37+F38+F39+F41)/($E29+$E30)*$E42</f>
+        <f t="shared" ref="F42:O42" si="18">(F29+F30+F31+F32+F33+F34+F36+F37+F38+F39+F41)/($E29+$E30)*$E42</f>
         <v>58072.727272727272</v>
       </c>
       <c r="G42" s="46">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>32942.727272727272</v>
       </c>
       <c r="H42" s="46">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>61372.727272727272</v>
       </c>
       <c r="I42" s="46">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>32942.727272727272</v>
       </c>
       <c r="J42" s="46">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>157541.81491303895</v>
       </c>
       <c r="K42" s="46">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>157541.81491303895</v>
       </c>
       <c r="L42" s="46">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>142284.41403991685</v>
       </c>
       <c r="M42" s="46">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>141574.72664381299</v>
       </c>
       <c r="N42" s="46">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>133591.17971374549</v>
       </c>
       <c r="O42" s="46">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>133591.17971374549</v>
       </c>
-      <c r="P42" s="30"/>
-      <c r="Q42" s="33">
+      <c r="P42" s="18">
+        <v>133591.18</v>
+      </c>
+      <c r="Q42" s="13">
+        <f t="shared" si="5"/>
+        <v>-2.8625450795516372E-4</v>
+      </c>
+      <c r="R42" s="33">
         <f>(K29+K30+K31+K32+K33+K34+K36+K37+K38+K39+K41)</f>
         <v>1732959.9640434284</v>
       </c>
-      <c r="R42" s="87"/>
       <c r="S42" s="87"/>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T42" s="87"/>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>64</v>
       </c>
@@ -4756,15 +4828,15 @@
         <f>(O36+O37+O38+O39)*$E43</f>
         <v>272042.13747024001</v>
       </c>
-      <c r="P43" s="30"/>
-      <c r="Q43" s="33">
-        <f>1825390.1-Q42</f>
+      <c r="Q43" s="30"/>
+      <c r="R43" s="33">
+        <f>1825390.1-R42</f>
         <v>92430.13595657167</v>
       </c>
-      <c r="R43" s="87"/>
       <c r="S43" s="87"/>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T43" s="87"/>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
         <v>65</v>
       </c>
@@ -4805,12 +4877,12 @@
       <c r="O44" s="46">
         <v>0</v>
       </c>
-      <c r="P44" s="30"/>
-      <c r="Q44" s="87"/>
+      <c r="Q44" s="30"/>
       <c r="R44" s="87"/>
       <c r="S44" s="87"/>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T44" s="87"/>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
         <v>49</v>
       </c>
@@ -4853,12 +4925,12 @@
       <c r="O45" s="46">
         <v>0</v>
       </c>
-      <c r="P45" s="30"/>
-      <c r="Q45" s="87"/>
+      <c r="Q45" s="30"/>
       <c r="R45" s="87"/>
       <c r="S45" s="87"/>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T45" s="87"/>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="8"/>
       <c r="B46" s="42"/>
       <c r="C46" s="43"/>
@@ -4881,7 +4953,7 @@
       </c>
       <c r="S46" s="87"/>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
         <v>72</v>
       </c>
@@ -4890,43 +4962,43 @@
       <c r="D47" s="12"/>
       <c r="E47" s="6"/>
       <c r="F47" s="6">
-        <f t="shared" ref="F47:O47" si="18">SUM(F29:F45)</f>
+        <f t="shared" ref="F47:O47" si="19">SUM(F29:F45)</f>
         <v>4305118.5388799999</v>
       </c>
       <c r="G47" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>4305037.5255239988</v>
       </c>
       <c r="H47" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>9170029.4601599984</v>
       </c>
       <c r="I47" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>5762302.7011200003</v>
       </c>
       <c r="J47" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3457348.6550399996</v>
       </c>
       <c r="K47" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1982932.7542684672</v>
       </c>
       <c r="L47" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1790600.8462598026</v>
       </c>
       <c r="M47" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1782084.597506556</v>
       </c>
       <c r="N47" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1681660.4855801458</v>
       </c>
       <c r="O47" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1953702.6230503859</v>
       </c>
       <c r="P47" s="30"/>
@@ -4937,7 +5009,7 @@
       </c>
       <c r="S47" s="87"/>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>73</v>
       </c>
@@ -4946,43 +5018,43 @@
       <c r="D48" s="12"/>
       <c r="E48" s="6"/>
       <c r="F48" s="6">
-        <f t="shared" ref="F48:O48" si="19">+F47/$C$10*$C$11</f>
+        <f t="shared" ref="F48:O48" si="20">+F47/$C$10*$C$11</f>
         <v>10045276.59072</v>
       </c>
       <c r="G48" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>10045087.559555996</v>
       </c>
       <c r="H48" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>21396735.407039996</v>
       </c>
       <c r="I48" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>13445372.969280001</v>
       </c>
       <c r="J48" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>8067146.8617599988</v>
       </c>
       <c r="K48" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4626843.0932930904</v>
       </c>
       <c r="L48" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4178068.6412728722</v>
       </c>
       <c r="M48" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4158197.3941819635</v>
       </c>
       <c r="N48" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3923874.4663536735</v>
       </c>
       <c r="O48" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4558639.4537842339</v>
       </c>
       <c r="P48" s="1"/>
@@ -5001,43 +5073,43 @@
       <c r="D49" s="12"/>
       <c r="E49" s="6"/>
       <c r="F49" s="6">
-        <f t="shared" ref="F49:O49" si="20">+F47+F48</f>
+        <f t="shared" ref="F49:O49" si="21">+F47+F48</f>
         <v>14350395.1296</v>
       </c>
       <c r="G49" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>14350125.085079994</v>
       </c>
       <c r="H49" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>30566764.867199995</v>
       </c>
       <c r="I49" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>19207675.670400001</v>
       </c>
       <c r="J49" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>11524495.516799998</v>
       </c>
       <c r="K49" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>6609775.8475615578</v>
       </c>
       <c r="L49" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5968669.4875326753</v>
       </c>
       <c r="M49" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5940281.9916885197</v>
       </c>
       <c r="N49" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5605534.9519338198</v>
       </c>
       <c r="O49" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>6512342.07683462</v>
       </c>
       <c r="P49" s="1"/>
@@ -5057,43 +5129,43 @@
         <v>0.11</v>
       </c>
       <c r="F50" s="46">
-        <f t="shared" ref="F50:O50" si="21">MIN(F47,$D50)*$E50</f>
+        <f t="shared" ref="F50:O50" si="22">MIN(F47,$D50)*$E50</f>
         <v>473563.0392768</v>
       </c>
       <c r="G50" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>473554.12780763989</v>
       </c>
       <c r="H50" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>496052.41510000004</v>
       </c>
       <c r="I50" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>496052.41510000004</v>
       </c>
       <c r="J50" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>380308.35205439996</v>
       </c>
       <c r="K50" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>218122.60296953141</v>
       </c>
       <c r="L50" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>196966.09308857829</v>
       </c>
       <c r="M50" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>196029.30572572115</v>
       </c>
       <c r="N50" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>184982.65341381604</v>
       </c>
       <c r="O50" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>214907.28853554244</v>
       </c>
       <c r="P50" s="13"/>
@@ -5113,43 +5185,43 @@
         <v>0.03</v>
       </c>
       <c r="F51" s="46">
-        <f t="shared" ref="F51:O51" si="22">MIN(F47,$D51)*$E51</f>
+        <f t="shared" ref="F51:O51" si="23">MIN(F47,$D51)*$E51</f>
         <v>129153.5561664</v>
       </c>
       <c r="G51" s="46">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>129151.12576571996</v>
       </c>
       <c r="H51" s="46">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>135287.02230000001</v>
       </c>
       <c r="I51" s="46">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>135287.02230000001</v>
       </c>
       <c r="J51" s="46">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>103720.45965119998</v>
       </c>
       <c r="K51" s="46">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>59487.982628054015</v>
       </c>
       <c r="L51" s="46">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>53718.025387794078</v>
       </c>
       <c r="M51" s="46">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>53462.537925196673</v>
       </c>
       <c r="N51" s="46">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>50449.814567404377</v>
       </c>
       <c r="O51" s="46">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>58611.078691511575</v>
       </c>
       <c r="P51" s="13"/>
@@ -5169,43 +5241,43 @@
         <v>0.03</v>
       </c>
       <c r="F52" s="46">
-        <f t="shared" ref="F52:O52" si="23">MIN(F49,$D52)*$E52</f>
+        <f t="shared" ref="F52:O52" si="24">MIN(F49,$D52)*$E52</f>
         <v>135287.02230000001</v>
       </c>
       <c r="G52" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>135287.02230000001</v>
       </c>
       <c r="H52" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>135287.02230000001</v>
       </c>
       <c r="I52" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>135287.02230000001</v>
       </c>
       <c r="J52" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>135287.02230000001</v>
       </c>
       <c r="K52" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>135287.02230000001</v>
       </c>
       <c r="L52" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>135287.02230000001</v>
       </c>
       <c r="M52" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>135287.02230000001</v>
       </c>
       <c r="N52" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>135287.02230000001</v>
       </c>
       <c r="O52" s="46">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>135287.02230000001</v>
       </c>
       <c r="P52" s="13"/>
@@ -5237,27 +5309,27 @@
         <v>864345.40516800003</v>
       </c>
       <c r="J53" s="46">
-        <f t="shared" ref="J53:O53" si="24">+J49*4/100</f>
+        <f t="shared" ref="J53:O53" si="25">+J49*4/100</f>
         <v>460979.82067199989</v>
       </c>
       <c r="K53" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>264391.03390246234</v>
       </c>
       <c r="L53" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>238746.779501307</v>
       </c>
       <c r="M53" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>237611.2796675408</v>
       </c>
       <c r="N53" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>224221.39807735279</v>
       </c>
       <c r="O53" s="46">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>260493.6830733848</v>
       </c>
       <c r="P53" s="13"/>
@@ -5300,11 +5372,11 @@
       <c r="D55" s="12"/>
       <c r="E55" s="6"/>
       <c r="F55" s="6">
-        <f t="shared" ref="F55:G55" si="25">SUM(F50:F54)</f>
+        <f t="shared" ref="F55:G55" si="26">SUM(F50:F54)</f>
         <v>1096763.4959831999</v>
       </c>
       <c r="G55" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1383747.9047019593</v>
       </c>
       <c r="H55" s="6">
@@ -5312,31 +5384,31 @@
         <v>4834269.606639999</v>
       </c>
       <c r="I55" s="6">
-        <f t="shared" ref="I55:O55" si="26">SUM(I50:I54)</f>
+        <f t="shared" ref="I55:O55" si="27">SUM(I50:I54)</f>
         <v>1630971.8648680001</v>
       </c>
       <c r="J55" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1080295.6546775999</v>
       </c>
       <c r="K55" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>677288.64180004783</v>
       </c>
       <c r="L55" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>624717.92027767934</v>
       </c>
       <c r="M55" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>622390.14561845863</v>
       </c>
       <c r="N55" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>594940.8883585732</v>
       </c>
       <c r="O55" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>669299.07260043884</v>
       </c>
       <c r="P55" s="1"/>
@@ -5356,39 +5428,39 @@
         <v>13253631.633616799</v>
       </c>
       <c r="G56" s="6">
-        <f t="shared" ref="G56:O56" si="27">+G49-G55</f>
+        <f t="shared" ref="G56:O56" si="28">+G49-G55</f>
         <v>12966377.180378035</v>
       </c>
       <c r="H56" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>25732495.260559995</v>
       </c>
       <c r="I56" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>17576703.805532001</v>
       </c>
       <c r="J56" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>10444199.862122398</v>
       </c>
       <c r="K56" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>5932487.2057615099</v>
       </c>
       <c r="L56" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>5343951.5672549959</v>
       </c>
       <c r="M56" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>5317891.8460700614</v>
       </c>
       <c r="N56" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>5010594.0635752464</v>
       </c>
       <c r="O56" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>5843043.0042341808</v>
       </c>
       <c r="P56" s="13"/>
@@ -5412,39 +5484,39 @@
         <v>462906.97030137602</v>
       </c>
       <c r="G57" s="46">
-        <f t="shared" ref="G57:O60" si="28">+(G$47-$D57)*$E57</f>
+        <f t="shared" ref="G57:O60" si="29">+(G$47-$D57)*$E57</f>
         <v>462898.24516293471</v>
       </c>
       <c r="H57" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>986857.87652323185</v>
       </c>
       <c r="I57" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>619845.70457462408</v>
       </c>
       <c r="J57" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>371602.15381180798</v>
       </c>
       <c r="K57" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>212807.56129871393</v>
       </c>
       <c r="L57" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>192093.41480618075</v>
       </c>
       <c r="M57" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>191176.2148154561</v>
       </c>
       <c r="N57" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>180360.53796098172</v>
       </c>
       <c r="O57" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>209659.47616652658</v>
       </c>
       <c r="P57" s="13"/>
@@ -5464,43 +5536,43 @@
         <v>1.5900000000000001E-2</v>
       </c>
       <c r="F58" s="46">
-        <f t="shared" ref="F58:F60" si="29">+(F$47-$D58)*$E58</f>
+        <f t="shared" ref="F58:F60" si="30">+(F$47-$D58)*$E58</f>
         <v>68340.02625619201</v>
       </c>
       <c r="G58" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>68338.738143831593</v>
       </c>
       <c r="H58" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>145692.10990454399</v>
       </c>
       <c r="I58" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>91509.254435808019</v>
       </c>
       <c r="J58" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>54860.485103135994</v>
       </c>
       <c r="K58" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>31417.27228086863</v>
       </c>
       <c r="L58" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>28359.194943530863</v>
       </c>
       <c r="M58" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>28223.786588354244</v>
       </c>
       <c r="N58" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>26627.043208724321</v>
       </c>
       <c r="O58" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>30952.513194501138</v>
       </c>
       <c r="P58" s="13"/>
@@ -5520,43 +5592,43 @@
         <v>4.7E-2</v>
       </c>
       <c r="F59" s="46">
+        <f t="shared" si="30"/>
+        <v>202011.39836736</v>
+      </c>
+      <c r="G59" s="46">
         <f t="shared" si="29"/>
-        <v>202011.39836736</v>
-      </c>
-      <c r="G59" s="46">
-        <f t="shared" si="28"/>
         <v>202007.59073962795</v>
       </c>
       <c r="H59" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>430662.21166751994</v>
       </c>
       <c r="I59" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>270499.05399264005</v>
       </c>
       <c r="J59" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>162166.21382687998</v>
       </c>
       <c r="K59" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>92868.666490617965</v>
       </c>
       <c r="L59" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>83829.066814210732</v>
       </c>
       <c r="M59" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>83428.803122808138</v>
       </c>
       <c r="N59" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>78708.86986226686</v>
       </c>
       <c r="O59" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>91494.85032336814</v>
       </c>
       <c r="P59" s="13"/>
@@ -5576,43 +5648,43 @@
         <v>9.4000000000000004E-3</v>
       </c>
       <c r="F60" s="46">
+        <f t="shared" si="30"/>
+        <v>40402.279673472003</v>
+      </c>
+      <c r="G60" s="46">
         <f t="shared" si="29"/>
-        <v>40402.279673472003</v>
-      </c>
-      <c r="G60" s="46">
-        <f t="shared" si="28"/>
         <v>40401.518147925592</v>
       </c>
       <c r="H60" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>86132.44233350399</v>
       </c>
       <c r="I60" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>54099.810798528008</v>
       </c>
       <c r="J60" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>32433.242765375995</v>
       </c>
       <c r="K60" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>18573.733298123592</v>
       </c>
       <c r="L60" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>16765.813362842146</v>
       </c>
       <c r="M60" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>16685.760624561626</v>
       </c>
       <c r="N60" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>15741.773972453373</v>
       </c>
       <c r="O60" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>18298.970064673627</v>
       </c>
       <c r="P60" s="13"/>
@@ -5634,39 +5706,39 @@
         <v>86102.370777599994</v>
       </c>
       <c r="G61" s="46">
-        <f t="shared" ref="G61:O61" si="30">+G$47*$E61</f>
+        <f t="shared" ref="G61:O61" si="31">+G$47*$E61</f>
         <v>86100.750510479978</v>
       </c>
       <c r="H61" s="46">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>183400.58920319998</v>
       </c>
       <c r="I61" s="46">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>115246.05402240001</v>
       </c>
       <c r="J61" s="46">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>69146.973100799994</v>
       </c>
       <c r="K61" s="46">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>39658.655085369348</v>
       </c>
       <c r="L61" s="46">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>35812.016925196054</v>
       </c>
       <c r="M61" s="46">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>35641.69195013112</v>
       </c>
       <c r="N61" s="46">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>33633.209711602918</v>
       </c>
       <c r="O61" s="46">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>39074.052461007719</v>
       </c>
       <c r="P61" s="13"/>
@@ -5688,39 +5760,39 @@
         <v>861023.70777599991</v>
       </c>
       <c r="G62" s="46">
-        <f t="shared" ref="G62:O63" si="31">+G$49*$E62</f>
+        <f t="shared" ref="G62:O63" si="32">+G$49*$E62</f>
         <v>861007.50510479964</v>
       </c>
       <c r="H62" s="46">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1834005.8920319995</v>
       </c>
       <c r="I62" s="46">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1152460.5402240001</v>
       </c>
       <c r="J62" s="46">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>691469.73100799986</v>
       </c>
       <c r="K62" s="46">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>396586.55085369345</v>
       </c>
       <c r="L62" s="46">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>358120.16925196053</v>
       </c>
       <c r="M62" s="46">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>356416.91950131115</v>
       </c>
       <c r="N62" s="46">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>336332.09711602918</v>
       </c>
       <c r="O62" s="46">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>390740.52461007721</v>
       </c>
       <c r="P62" s="13"/>
@@ -5742,39 +5814,39 @@
         <v>1061929.2395903999</v>
       </c>
       <c r="G63" s="46">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1061909.2562959194</v>
       </c>
       <c r="H63" s="46">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>2261940.6001727995</v>
       </c>
       <c r="I63" s="46">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1421367.9996096001</v>
       </c>
       <c r="J63" s="46">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>852812.66824319982</v>
       </c>
       <c r="K63" s="46">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>489123.41271955526</v>
       </c>
       <c r="L63" s="46">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>441681.54207741795</v>
       </c>
       <c r="M63" s="46">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>439580.86738495046</v>
       </c>
       <c r="N63" s="46">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>414809.58644310263</v>
       </c>
       <c r="O63" s="46">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>481913.31368576188</v>
       </c>
       <c r="P63" s="13"/>
@@ -5796,39 +5868,39 @@
         <v>1827</v>
       </c>
       <c r="G64" s="46">
-        <f t="shared" ref="G64:O65" si="32">+$D64</f>
+        <f t="shared" ref="G64:O65" si="33">+$D64</f>
         <v>1827</v>
       </c>
       <c r="H64" s="46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>1827</v>
       </c>
       <c r="I64" s="46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>1827</v>
       </c>
       <c r="J64" s="46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>1827</v>
       </c>
       <c r="K64" s="46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>1827</v>
       </c>
       <c r="L64" s="46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>1827</v>
       </c>
       <c r="M64" s="46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>1827</v>
       </c>
       <c r="N64" s="46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>1827</v>
       </c>
       <c r="O64" s="46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>1827</v>
       </c>
       <c r="P64" s="13"/>
@@ -5850,39 +5922,39 @@
         <v>424.62</v>
       </c>
       <c r="G65" s="46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>424.62</v>
       </c>
       <c r="H65" s="46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>424.62</v>
       </c>
       <c r="I65" s="46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>424.62</v>
       </c>
       <c r="J65" s="46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>424.62</v>
       </c>
       <c r="K65" s="46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>424.62</v>
       </c>
       <c r="L65" s="46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>424.62</v>
       </c>
       <c r="M65" s="46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>424.62</v>
       </c>
       <c r="N65" s="46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>424.62</v>
       </c>
       <c r="O65" s="46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>424.62</v>
       </c>
       <c r="P65" s="13"/>
@@ -5908,23 +5980,23 @@
         <v>21900</v>
       </c>
       <c r="K66" s="46">
-        <f t="shared" ref="K66:O66" si="33">+$D66*$C$9</f>
+        <f t="shared" ref="K66:O66" si="34">+$D66*$C$9</f>
         <v>21900</v>
       </c>
       <c r="L66" s="46">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>21900</v>
       </c>
       <c r="M66" s="46">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>21900</v>
       </c>
       <c r="N66" s="46">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>21900</v>
       </c>
       <c r="O66" s="46">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>21900</v>
       </c>
       <c r="P66" s="13"/>
@@ -5933,9 +6005,9 @@
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="8"/>
-      <c r="B67" s="107"/>
-      <c r="C67" s="107"/>
-      <c r="D67" s="108"/>
+      <c r="B67" s="110"/>
+      <c r="C67" s="110"/>
+      <c r="D67" s="111"/>
       <c r="E67" s="49"/>
       <c r="F67" s="46"/>
       <c r="G67" s="46"/>
@@ -5960,43 +6032,43 @@
       <c r="D68" s="12"/>
       <c r="E68" s="6"/>
       <c r="F68" s="6">
-        <f t="shared" ref="F68:O68" si="34">SUM(F57:F67)</f>
+        <f t="shared" ref="F68:O68" si="35">SUM(F57:F67)</f>
         <v>2784967.6127423998</v>
       </c>
       <c r="G68" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2784915.2241055192</v>
       </c>
       <c r="H68" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>5930943.3418367999</v>
       </c>
       <c r="I68" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>3727280.0376576008</v>
       </c>
       <c r="J68" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2258643.0878591994</v>
       </c>
       <c r="K68" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1305187.4720269423</v>
       </c>
       <c r="L68" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1180812.8381813392</v>
       </c>
       <c r="M68" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1175305.663987573</v>
       </c>
       <c r="N68" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1110364.7382751612</v>
       </c>
       <c r="O68" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1286285.3205059166</v>
       </c>
       <c r="P68" s="1"/>
@@ -6012,43 +6084,43 @@
       <c r="D69" s="12"/>
       <c r="E69" s="6"/>
       <c r="F69" s="6">
-        <f t="shared" ref="F69:O69" si="35">+F49+F68</f>
+        <f t="shared" ref="F69:O69" si="36">+F49+F68</f>
         <v>17135362.742342398</v>
       </c>
       <c r="G69" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>17135040.309185512</v>
       </c>
       <c r="H69" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>36497708.209036797</v>
       </c>
       <c r="I69" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>22934955.708057601</v>
       </c>
       <c r="J69" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>13783138.604659196</v>
       </c>
       <c r="K69" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>7914963.3195885001</v>
       </c>
       <c r="L69" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>7149482.3257140145</v>
       </c>
       <c r="M69" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>7115587.655676093</v>
       </c>
       <c r="N69" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>6715899.6902089808</v>
       </c>
       <c r="O69" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>7798627.3973405361</v>
       </c>
       <c r="P69" s="1"/>
